--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CB ARIDANE.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CB ARIDANE.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8422</v>
+        <v>3.9014</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5216</v>
+        <v>5.7866</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6794</v>
+        <v>-1.8852</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5856</v>
+        <v>2.6794</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6765</v>
+        <v>0.7765</v>
       </c>
       <c r="I2" t="n">
-        <v>1.9091</v>
+        <v>1.9029</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0083</v>
+        <v>4.2385</v>
       </c>
       <c r="K2" t="n">
-        <v>2.1266</v>
+        <v>2.3094</v>
       </c>
       <c r="L2" t="n">
-        <v>1.8816</v>
+        <v>1.9292</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.4227</v>
+        <v>-1.5591</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.4501</v>
+        <v>-1.5329</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0274</v>
+        <v>-0.0262</v>
       </c>
       <c r="P2" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5563</v>
+        <v>0.5562</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6581</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0974</v>
+        <v>-0.1019</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.7</v>
+        <v>-0.6974</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8597</v>
+        <v>0.89</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.5597</v>
+        <v>-1.5874</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0296</v>
+        <v>3.1094</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6276</v>
+        <v>4.9418</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.598</v>
+        <v>-1.8324</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2482</v>
+        <v>3.3058</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0069</v>
+        <v>0.0118</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2552</v>
+        <v>3.294</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7284</v>
+        <v>4.9438</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6431</v>
+        <v>1.7499</v>
       </c>
       <c r="L3" t="n">
-        <v>3.0853</v>
+        <v>3.1939</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4802</v>
+        <v>-1.638</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.6501</v>
+        <v>-1.7381</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1699</v>
+        <v>0.1001</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3218</v>
+        <v>0.3031</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4402</v>
+        <v>0.4449</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1184</v>
+        <v>-0.1418</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4596</v>
+        <v>1.5005</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.996</v>
+        <v>1.9529</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9607</v>
+        <v>4.1127</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.9646</v>
+        <v>-2.1598</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5087</v>
+        <v>-0.5216</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7623</v>
+        <v>0.7574</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.2711</v>
+        <v>-1.279</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3851</v>
+        <v>2.5086</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8195</v>
+        <v>1.8679</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5656</v>
+        <v>0.6407</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.8938</v>
+        <v>-3.0302</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0571</v>
+        <v>-1.1105</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.8367</v>
+        <v>-1.9197</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8647</v>
+        <v>0.8408</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3758</v>
+        <v>0.383</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4889</v>
+        <v>0.4578</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8398</v>
+        <v>0.8547</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3599</v>
+        <v>-0.3663</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7374</v>
+        <v>1.6091</v>
       </c>
       <c r="E5" t="n">
-        <v>5.062</v>
+        <v>5.13</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.3246</v>
+        <v>-3.5208</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.906</v>
+        <v>-1.9573</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.598</v>
+        <v>-0.5824</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.308</v>
+        <v>-1.3749</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1234</v>
+        <v>1.2057</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3235</v>
+        <v>0.3952</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.8105</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.0294</v>
+        <v>-3.1631</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9215</v>
+        <v>-0.9776</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.1079</v>
+        <v>-2.1855</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3833</v>
+        <v>3.3133</v>
       </c>
       <c r="T5" t="n">
-        <v>3.7591</v>
+        <v>3.6963</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3758</v>
+        <v>-0.383</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3401</v>
+        <v>-0.3311</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1795</v>
+        <v>0.2279</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -877,28 +877,28 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -955,28 +955,28 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2999</v>
+        <v>0.3079</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6412</v>
+        <v>-0.6449</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7579</v>
+        <v>0.9516</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3991</v>
+        <v>-1.5965</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0333</v>
+        <v>-0.0287</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3488</v>
+        <v>2.3672</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.3821</v>
+        <v>-2.3958</v>
       </c>
       <c r="J8" t="n">
-        <v>2.325</v>
+        <v>2.4633</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9991</v>
+        <v>3.079</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6742</v>
+        <v>-0.6156</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.3583</v>
+        <v>-2.492</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6503</v>
+        <v>-0.7118</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.7079</v>
+        <v>-1.7802</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.4004</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8124</v>
+        <v>0.7822</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4335</v>
+        <v>0.4356</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3789</v>
+        <v>0.3465</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.0198</v>
+        <v>-0.0353</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.0198</v>
+        <v>-0.0353</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. JIMENEZ BARRETO</t>
+          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9353</v>
+        <v>-1.0311</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2512</v>
+        <v>-1.4874</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6840000000000001</v>
+        <v>0.4563</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1011</v>
+        <v>-3.2388</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.426</v>
+        <v>-2.8967</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3249</v>
+        <v>-0.3421</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1999</v>
+        <v>-1.4191</v>
       </c>
       <c r="K9" t="n">
-        <v>0.16</v>
+        <v>-1.5085</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3011</v>
+        <v>-1.8196</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.586</v>
+        <v>-1.3881</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2849</v>
+        <v>-0.4315</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4001</v>
+        <v>1.3632</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4001</v>
+        <v>1.3632</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3746</v>
+        <v>0.1824</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4512</v>
+        <v>-0.0683</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0766</v>
+        <v>0.2507</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8597</v>
+        <v>0.6621</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8597</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
+          <t>A. JIMENEZ BARRETO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9747</v>
+        <v>-1.0503</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6373</v>
+        <v>-0.2281</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6626</v>
+        <v>-0.8222</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2425</v>
+        <v>-0.182</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.9138</v>
+        <v>-0.4752</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3287</v>
+        <v>0.2932</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5485</v>
+        <v>0.2047</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.5923</v>
+        <v>0.1642</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0438</v>
+        <v>0.0405</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6939</v>
+        <v>-0.3868</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3214</v>
+        <v>-0.6394</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3725</v>
+        <v>0.2527</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4004</v>
+        <v>0.3895</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4004</v>
+        <v>0.3895</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1872</v>
+        <v>-0.3678</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0888</v>
+        <v>-0.4328</v>
       </c>
       <c r="U10" t="n">
-        <v>0.276</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6802</v>
+        <v>-0.89</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6802</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4915</v>
+        <v>-1.3228</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3688</v>
+        <v>2.7763</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.8603</v>
+        <v>-4.0991</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2974</v>
+        <v>-0.1551</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6603</v>
+        <v>2.8194</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.9577</v>
+        <v>-2.9745</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6537</v>
+        <v>3.975</v>
       </c>
       <c r="K11" t="n">
-        <v>4.246</v>
+        <v>4.4852</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5923</v>
+        <v>-0.5101</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.9511</v>
+        <v>-4.1301</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5857</v>
+        <v>-1.6658</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.3654</v>
+        <v>-2.4644</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2461</v>
+        <v>0.2502</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.8002</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5498</v>
+        <v>-0.55</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0401</v>
+        <v>-1.0284</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.0803</v>
+        <v>-0.0516</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.9598</v>
+        <v>-0.9768</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1842</v>
+        <v>-4.2452</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6257</v>
+        <v>-2.5179</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5585</v>
+        <v>-1.7273</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.6242</v>
+        <v>-4.6548</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3799</v>
+        <v>-0.39</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.2444</v>
+        <v>-4.2648</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8522</v>
+        <v>-1.7759</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1418</v>
+        <v>0.1771</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.994</v>
+        <v>-1.953</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.772</v>
+        <v>-2.8789</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.5671</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.2503</v>
+        <v>-2.3118</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0002</v>
+        <v>-0.003</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7735</v>
+        <v>-0.742</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7732</v>
+        <v>0.739</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3599</v>
+        <v>-0.3663</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3599</v>
+        <v>-0.3663</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.7292</v>
+        <v>-4.6859</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.163</v>
+        <v>-2.8919</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5662</v>
+        <v>-1.794</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4111</v>
+        <v>-0.4142</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5849</v>
+        <v>0.5501</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9961</v>
+        <v>-0.9643</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9472</v>
+        <v>1.0725</v>
       </c>
       <c r="K13" t="n">
-        <v>1.6995</v>
+        <v>1.7447</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7523</v>
+        <v>-0.6722</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3583</v>
+        <v>-1.4867</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1146</v>
+        <v>-1.1947</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2438</v>
+        <v>-0.292</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.8008</v>
+        <v>-2.7263</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3175</v>
+        <v>-0.3243</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.709</v>
+        <v>-0.6802</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3915</v>
+        <v>0.3559</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.7997</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.4512</v>
+        <v>-1.483699999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>15.5211</v>
+        <v>17.4974</v>
       </c>
       <c r="F14" t="n">
-        <v>-16.9721</v>
+        <v>-18.981</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.3908</v>
+        <v>-4.2436</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6079</v>
+        <v>3.8618</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.9989</v>
+        <v>-8.1053</v>
       </c>
       <c r="J14" t="n">
-        <v>16.87</v>
+        <v>18.34080000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>14.4665</v>
+        <v>15.3878</v>
       </c>
       <c r="L14" t="n">
-        <v>2.4034</v>
+        <v>2.9533</v>
       </c>
       <c r="M14" t="n">
-        <v>-21.2608</v>
+        <v>-22.5845</v>
       </c>
       <c r="N14" t="n">
-        <v>-10.8585</v>
+        <v>-11.526</v>
       </c>
       <c r="O14" t="n">
-        <v>-10.4023</v>
+        <v>-11.0585</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-10.0029</v>
+        <v>-9.7369</v>
       </c>
       <c r="R14" t="n">
-        <v>10.0028</v>
+        <v>9.736800000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>5.6795</v>
+        <v>5.5331</v>
       </c>
       <c r="T14" t="n">
-        <v>4.435700000000001</v>
+        <v>4.4948</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2437</v>
+        <v>1.0383</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.7396</v>
+        <v>-2.7733</v>
       </c>
       <c r="W14" t="n">
-        <v>4.2182</v>
+        <v>4.398400000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.957699999999999</v>
+        <v>-7.1717</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CB ARIDANE.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CB ARIDANE.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. MEJIA ACOSTA</t>
+          <t>O. BALSELLS PLAZA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9014</v>
+        <v>3.7731</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7866</v>
+        <v>5.6396</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.8852</v>
+        <v>-1.8665</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6794</v>
+        <v>3.3058</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7765</v>
+        <v>0.0118</v>
       </c>
       <c r="I2" t="n">
-        <v>1.9029</v>
+        <v>3.294</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2385</v>
+        <v>4.9438</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3094</v>
+        <v>1.7499</v>
       </c>
       <c r="L2" t="n">
-        <v>1.9292</v>
+        <v>3.1939</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.5591</v>
+        <v>-1.638</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.5329</v>
+        <v>-1.7381</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0262</v>
+        <v>0.1001</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3632</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3632</v>
+        <v>1.1684</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5562</v>
+        <v>0.9668</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6581</v>
+        <v>1.1426</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1019</v>
+        <v>-0.1758</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.6974</v>
+        <v>0.2795</v>
       </c>
       <c r="W2" t="n">
-        <v>0.89</v>
+        <v>1.5005</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.5874</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O. BALSELLS PLAZA</t>
+          <t>G. MEJIA ACOSTA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1094</v>
+        <v>3.7485</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9418</v>
+        <v>5.1885</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.8324</v>
+        <v>-1.44</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3058</v>
+        <v>2.6794</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0118</v>
+        <v>0.7765</v>
       </c>
       <c r="I3" t="n">
-        <v>3.294</v>
+        <v>1.9029</v>
       </c>
       <c r="J3" t="n">
-        <v>4.9438</v>
+        <v>4.2385</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7499</v>
+        <v>2.3094</v>
       </c>
       <c r="L3" t="n">
-        <v>3.1939</v>
+        <v>1.9292</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.638</v>
+        <v>-1.5591</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.7381</v>
+        <v>-1.5329</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1001</v>
+        <v>-0.0262</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7789</v>
+        <v>1.3632</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9474</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1684</v>
+        <v>1.3632</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3031</v>
+        <v>0.4033</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4449</v>
+        <v>0.06</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1418</v>
+        <v>0.3433</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2795</v>
+        <v>-0.6974</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5005</v>
+        <v>0.89</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2211</v>
+        <v>-1.5874</v>
       </c>
     </row>
     <row r="4">
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9529</v>
+        <v>2.551</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1127</v>
+        <v>4.7107</v>
       </c>
       <c r="F4" t="n">
         <v>-2.1598</v>
@@ -766,10 +766,10 @@
         <v>0.7789</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8408</v>
+        <v>1.4388</v>
       </c>
       <c r="T4" t="n">
-        <v>0.383</v>
+        <v>0.9811</v>
       </c>
       <c r="U4" t="n">
         <v>0.4578</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. VIERA LOPEZ</t>
+          <t>G. MEJÍA ACOSTA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6091</v>
+        <v>0.6158</v>
       </c>
       <c r="E5" t="n">
-        <v>5.13</v>
+        <v>0.6158</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.5208</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.9573</v>
+        <v>0.6158</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5824</v>
+        <v>0.6158</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3749</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2057</v>
+        <v>0.6158</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3952</v>
+        <v>0.6158</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8105</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.1631</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9776</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.1855</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5842000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5842000000000001</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3133</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.6963</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.383</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3311</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2279</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5590000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. MEJÍA ACOSTA</t>
+          <t>J. GONZÁLEZ CHÁVEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,28 +877,28 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6158</v>
+        <v>0.3079</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6158</v>
+        <v>0.3079</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6158</v>
+        <v>0.3079</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6158</v>
+        <v>0.3079</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6158</v>
+        <v>0.3079</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6158</v>
+        <v>0.3079</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. GONZÁLEZ CHÁVEZ</t>
+          <t>D. VIERA LOPEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3079</v>
+        <v>-0.2515</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3079</v>
+        <v>3.1364</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-3.3879</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3079</v>
+        <v>-1.9573</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3079</v>
+        <v>-0.5824</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-1.3749</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3079</v>
+        <v>1.2057</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3079</v>
+        <v>0.3952</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.8105</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-3.1631</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.9776</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-2.1855</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.4527</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.7028</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.2501</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.3311</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2279</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6449</v>
+        <v>-0.4518</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9516</v>
+        <v>1.151</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5965</v>
+        <v>-1.6027</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0287</v>
@@ -1078,13 +1078,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7822</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4356</v>
+        <v>0.635</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3465</v>
+        <v>0.3403</v>
       </c>
       <c r="V8" t="n">
         <v>-0.0353</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
+          <t>A. GASE SECO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0311</v>
+        <v>-0.6845</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4874</v>
+        <v>2.9756</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4563</v>
+        <v>-3.6601</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.2388</v>
+        <v>-0.1551</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.8967</v>
+        <v>2.8194</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3421</v>
+        <v>-2.9745</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4191</v>
+        <v>3.975</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.5085</v>
+        <v>4.4852</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08939999999999999</v>
+        <v>-0.5101</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8196</v>
+        <v>-4.1301</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3881</v>
+        <v>-1.6658</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4315</v>
+        <v>-2.4644</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3632</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3632</v>
+        <v>1.5579</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1824</v>
+        <v>0.8885</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0683</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2507</v>
+        <v>-0.111</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6621</v>
+        <v>-1.0284</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.0516</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6621</v>
+        <v>-0.9768</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0503</v>
+        <v>-0.7119</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2281</v>
+        <v>-0.0288</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8222</v>
+        <v>-0.6831</v>
       </c>
       <c r="G10" t="n">
         <v>-0.182</v>
@@ -1234,13 +1234,13 @@
         <v>0.3895</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3678</v>
+        <v>-0.0293</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4328</v>
+        <v>-0.2335</v>
       </c>
       <c r="U10" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.2042</v>
       </c>
       <c r="V10" t="n">
         <v>-0.89</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. GASE SECO</t>
+          <t>G. PIERRE-GABRIEL ANDREA GASTON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3228</v>
+        <v>-0.9431</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7763</v>
+        <v>-1.2881</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.0991</v>
+        <v>0.345</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1551</v>
+        <v>-3.2388</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8194</v>
+        <v>-2.8967</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.9745</v>
+        <v>-0.3421</v>
       </c>
       <c r="J11" t="n">
-        <v>3.975</v>
+        <v>-1.4191</v>
       </c>
       <c r="K11" t="n">
-        <v>4.4852</v>
+        <v>-1.5085</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5101</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.1301</v>
+        <v>-1.8196</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.6658</v>
+        <v>-1.3881</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.4644</v>
+        <v>-0.4315</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3895</v>
+        <v>1.3632</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9474</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5579</v>
+        <v>1.3632</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2502</v>
+        <v>0.2704</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8002</v>
+        <v>0.1311</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.55</v>
+        <v>0.1393</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0284</v>
+        <v>0.6621</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.0516</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.9768</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2452</v>
+        <v>-4.1293</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5179</v>
+        <v>-2.3186</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7273</v>
+        <v>-1.8108</v>
       </c>
       <c r="G12" t="n">
         <v>-4.6548</v>
@@ -1390,13 +1390,13 @@
         <v>0.7789</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.003</v>
+        <v>0.1128</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.742</v>
+        <v>-0.5427</v>
       </c>
       <c r="U12" t="n">
-        <v>0.739</v>
+        <v>0.6555</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3663</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.6859</v>
+        <v>-4.6435</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8919</v>
+        <v>-2.5928</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.794</v>
+        <v>-2.0507</v>
       </c>
       <c r="G13" t="n">
         <v>-0.4142</v>
@@ -1468,13 +1468,13 @@
         <v>1.1684</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3243</v>
+        <v>-0.282</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6802</v>
+        <v>-0.3812</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3559</v>
+        <v>0.0992</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2211</v>
@@ -1501,25 +1501,25 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.483699999999999</v>
+        <v>-0.819300000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>17.4974</v>
+        <v>17.4972</v>
       </c>
       <c r="F14" t="n">
-        <v>-18.981</v>
+        <v>-18.3166</v>
       </c>
       <c r="G14" t="n">
         <v>-4.2436</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8618</v>
+        <v>3.861800000000001</v>
       </c>
       <c r="I14" t="n">
         <v>-8.1053</v>
       </c>
       <c r="J14" t="n">
-        <v>18.34080000000001</v>
+        <v>18.3408</v>
       </c>
       <c r="K14" t="n">
         <v>15.3878</v>
@@ -1546,13 +1546,13 @@
         <v>9.736800000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>5.5331</v>
+        <v>6.1973</v>
       </c>
       <c r="T14" t="n">
-        <v>4.4948</v>
+        <v>4.4947</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0383</v>
+        <v>1.7027</v>
       </c>
       <c r="V14" t="n">
         <v>-2.7733</v>
